--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N119_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N119_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.92425582933249</v>
+        <v>9.900191572266529</v>
       </c>
       <c r="D2" t="n">
-        <v>34.50219300731548</v>
+        <v>5.606606363688766</v>
       </c>
       <c r="E2" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F2" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.61371866288852</v>
+        <v>8.712229282719385</v>
       </c>
       <c r="D3" t="n">
-        <v>23.72226523265843</v>
+        <v>3.854868100306995</v>
       </c>
       <c r="E3" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F3" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.99730314616296</v>
+        <v>6.662061761251481</v>
       </c>
       <c r="D4" t="n">
-        <v>42.04088931894501</v>
+        <v>6.831644514328564</v>
       </c>
       <c r="E4" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F4" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.13008602367991</v>
+        <v>8.958638978847985</v>
       </c>
       <c r="D5" t="n">
-        <v>54.05554017720614</v>
+        <v>8.784025278795998</v>
       </c>
       <c r="E5" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F5" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.1565201554439</v>
+        <v>2.625434525259633</v>
       </c>
       <c r="D6" t="n">
-        <v>16.77006812928194</v>
+        <v>2.725136071008315</v>
       </c>
       <c r="E6" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F6" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.46585590250788</v>
+        <v>6.25070158415753</v>
       </c>
       <c r="D7" t="n">
-        <v>37.99374523998202</v>
+        <v>6.173983601497079</v>
       </c>
       <c r="E7" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F7" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>15.56280189771322</v>
+        <v>2.528955308378399</v>
       </c>
       <c r="D8" t="n">
-        <v>16.14463101862392</v>
+        <v>2.623502540526387</v>
       </c>
       <c r="E8" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F8" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>16.59758760923632</v>
+        <v>2.697107986500903</v>
       </c>
       <c r="D9" t="n">
-        <v>19.91253100576236</v>
+        <v>3.235786288436383</v>
       </c>
       <c r="E9" t="n">
-        <v>17.69609159207153</v>
+        <v>2.875614883711624</v>
       </c>
       <c r="F9" t="n">
-        <v>12.80959708832681</v>
+        <v>2.081559526853106</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
